--- a/results/naturverbundenheit/observables/nature-dataset-observable-patterns-auto.xlsx
+++ b/results/naturverbundenheit/observables/nature-dataset-observable-patterns-auto.xlsx
@@ -470,22 +470,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06710032090350081</v>
+        <v>0.2329066195676763</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6002859265210185</v>
+        <v>0.8009049274063303</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6020878023864188</v>
+        <v>0.9996786372198396</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7990993973715198</v>
+        <v>0.8000144461658997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8001253879606737</v>
+        <v>0.9998483795551151</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7997949135597545</v>
+        <v>0.9999188715738447</v>
       </c>
     </row>
     <row r="3">
@@ -493,22 +493,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4651983144525276</v>
+        <v>0.1816372722034393</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7992721124686959</v>
+        <v>0.8006036577714746</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9997051184327179</v>
+        <v>0.8005714656505235</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9979902959469111</v>
+        <v>0.7983096520499875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9995835757912188</v>
+        <v>0.8001820749312883</v>
       </c>
       <c r="G3" t="n">
-        <v>0.999789061116825</v>
+        <v>0.7997228431889463</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.33290390604123</v>
+        <v>0.6161760438540141</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9996003718040778</v>
+        <v>0.9986842062313819</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999000828818079</v>
+        <v>0.9997542086718897</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2003187108086564</v>
+        <v>0.9997923682734692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999375492813817</v>
+        <v>0.9998389868211328</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9999157034398435</v>
+        <v>0.99981938108119</v>
       </c>
     </row>
     <row r="5">
@@ -539,22 +539,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.283583688795428</v>
+        <v>0.1678762260143402</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9998180082170063</v>
+        <v>0.9998939713188491</v>
       </c>
       <c r="D5" t="n">
-        <v>0.999651580249128</v>
+        <v>0.9998019857701613</v>
       </c>
       <c r="E5" t="n">
-        <v>0.798839591027346</v>
+        <v>0.9998297124409112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999738447263273</v>
+        <v>0.9998153113046386</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9998727904193498</v>
+        <v>0.9997726379832002</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1668852083231664</v>
+        <v>-0.0003295436494725468</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9998142018218741</v>
+        <v>0.5999946592872787</v>
       </c>
       <c r="D6" t="n">
-        <v>0.999912161357583</v>
+        <v>0.6004209197764847</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9998235906751965</v>
+        <v>0.4004347845408849</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9997852803317806</v>
+        <v>0.5999899191791603</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9997021809328088</v>
+        <v>0.4007993125756488</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6657316772880129</v>
+        <v>0.2664788226827614</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9999077833992741</v>
+        <v>0.2004090581257112</v>
       </c>
       <c r="D7" t="n">
-        <v>0.999772993266973</v>
+        <v>1.000027936864756</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999121147014469</v>
+        <v>0.9996783418023283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999977276899438</v>
+        <v>0.9998954824573744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9999140702081297</v>
+        <v>1.000018836754969</v>
       </c>
     </row>
     <row r="8">
@@ -608,22 +608,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.2667508471484537</v>
+        <v>0.3672191205736182</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2010173465702564</v>
+        <v>0.7991324555913277</v>
       </c>
       <c r="D8" t="n">
-        <v>0.201762229089816</v>
+        <v>0.4003852157977469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2005544149751306</v>
+        <v>0.9985828742570229</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2012692339734456</v>
+        <v>0.9998823720351925</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2005418668919219</v>
+        <v>0.9997897109876615</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2176466894684979</v>
+        <v>0.3021659209402667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9993728834731656</v>
+        <v>0.9996212963575873</v>
       </c>
       <c r="D9" t="n">
-        <v>0.999556354241524</v>
+        <v>0.9998209924017942</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4001145667425028</v>
+        <v>0.2002817784458517</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7993882144978534</v>
+        <v>0.999956386797073</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7987156809099967</v>
+        <v>0.9998296781788416</v>
       </c>
     </row>
     <row r="10">
@@ -654,22 +654,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2835100875003626</v>
+        <v>0.5167967487242857</v>
       </c>
       <c r="C10" t="n">
-        <v>0.998679787796005</v>
+        <v>0.9993690770704932</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6003386348305422</v>
+        <v>0.9996895799919134</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8003748215245867</v>
+        <v>0.7989378109163535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9994524760222683</v>
+        <v>0.9997019095727491</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8010316642624216</v>
+        <v>0.9997101421602951</v>
       </c>
     </row>
   </sheetData>
